--- a/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/checklist-apertura-parrillero-asador-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/checklist-apertura-parrillero-asador-eventos.xlsx
@@ -1157,7 +1157,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Guarda 100 g de cada plato, identificados y fechados, a 4 °C o menos o congelados, durante 7 días: obligatoria en eventos de más de 40 personas y si los eventos son tu actividad principal (art. 30.8 y 30.10 del RD 1086/2020)</t>
+          <t>Guarda 100 g de cada plato, identificados y fechados, a 4 °C o menos o congelados, durante 7 días: obligatoria en todos tus eventos, porque son tu actividad principal (art. 30.8.d del RD 1086/2020), y en cualquier encargo de más de 40 personas (30.8.e); conservación según el 30.10</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Versión 2.2 · septiembre 2026 · aichef.pro/plan-negocio-parrillero-asador-eventos · info@aichef.pro</t>
+          <t>Versión 2.2 · octubre 2026 · aichef.pro/plan-negocio-parrillero-asador-eventos · info@aichef.pro</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/checklist-apertura-parrillero-asador-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/checklist-apertura-parrillero-asador-eventos.xlsx
@@ -951,8 +951,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1490,8 +1490,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19 A20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19 A20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1975,8 +1975,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2352,8 +2352,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2891,8 +2891,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19 A20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19 A20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -3403,8 +3403,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
